--- a/data/product-labels.xlsx
+++ b/data/product-labels.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,13 +418,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Starter GM 3.0 Hyster (Brand New)</v>
+        <v>Seal</v>
       </c>
       <c r="B2" t="str">
-        <v>1650426-NEW</v>
+        <v>HNXKCF-00017</v>
       </c>
       <c r="C2" t="str">
-        <v>091833290251</v>
+        <v>943577012450</v>
       </c>
       <c r="D2" t="str">
         <v>Bulldog Forklifts</v>
@@ -435,13 +435,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Starter Hyster # 4110035 GM PSI</v>
+        <v>Oil Seal Torque</v>
       </c>
       <c r="B3" t="str">
-        <v>4110035</v>
+        <v>32593-23630-71</v>
       </c>
       <c r="C3" t="str">
-        <v>479875395779</v>
+        <v>169159184314</v>
       </c>
       <c r="D3" t="str">
         <v>Bulldog Forklifts</v>
@@ -452,13 +452,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Starter (Heavy Duty) Hyster</v>
+        <v>Toyota Keys</v>
       </c>
       <c r="B4" t="str">
-        <v>1383240-HD</v>
+        <v>57591-23330-71</v>
       </c>
       <c r="C4" t="str">
-        <v>520992032063</v>
+        <v>936426911489</v>
       </c>
       <c r="D4" t="str">
         <v>Bulldog Forklifts</v>
@@ -469,13 +469,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Starter Yale/Hyster GM 2.4 L</v>
+        <v>Lower Liner</v>
       </c>
       <c r="B5" t="str">
-        <v>580044885</v>
+        <v>82152-25080-71</v>
       </c>
       <c r="C5" t="str">
-        <v>918215510983</v>
+        <v>199126568889</v>
       </c>
       <c r="D5" t="str">
         <v>Bulldog Forklifts</v>
@@ -486,13 +486,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Starter Bran New Hyster GM 2.4 L</v>
+        <v>Bearing - Needle</v>
       </c>
       <c r="B6" t="str">
-        <v>4250512-NEW</v>
+        <v>AS39374-3600</v>
       </c>
       <c r="C6" t="str">
-        <v>408728151411</v>
+        <v>577281619560</v>
       </c>
       <c r="D6" t="str">
         <v>Bulldog Forklifts</v>
@@ -503,13 +503,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Water Pump Hyster</v>
+        <v>Seat</v>
       </c>
       <c r="B7" t="str">
-        <v>1389100</v>
+        <v>4700</v>
       </c>
       <c r="C7" t="str">
-        <v>113372762872</v>
+        <v>701005431572</v>
       </c>
       <c r="D7" t="str">
         <v>Bulldog Forklifts</v>
@@ -520,13 +520,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Brake Shoe Set Hyster (2 Shoe)</v>
+        <v>Ecu - Gen 4</v>
       </c>
       <c r="B8" t="str">
-        <v>2026787</v>
+        <v>CI78725</v>
       </c>
       <c r="C8" t="str">
-        <v>211797619700</v>
+        <v>889817344256</v>
       </c>
       <c r="D8" t="str">
         <v>Bulldog Forklifts</v>
@@ -537,13 +537,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Cylinder Master Hyster</v>
+        <v>Hook Group</v>
       </c>
       <c r="B9" t="str">
-        <v>1347048</v>
+        <v>CA204182</v>
       </c>
       <c r="C9" t="str">
-        <v>326063756507</v>
+        <v>535529854190</v>
       </c>
       <c r="D9" t="str">
         <v>Bulldog Forklifts</v>
@@ -554,24 +554,585 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Cylinder Master Hyster</v>
+        <v>Bearing - Cone</v>
       </c>
       <c r="B10" t="str">
-        <v>1536724</v>
+        <v>HY0230325</v>
       </c>
       <c r="C10" t="str">
-        <v>871418219852</v>
+        <v>670939185656</v>
       </c>
       <c r="D10" t="str">
         <v>Bulldog Forklifts</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Switch</v>
+      </c>
+      <c r="B11" t="str">
+        <v>KO2EB-55-21980</v>
+      </c>
+      <c r="C11" t="str">
+        <v>236829076374</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Fuel Cap</v>
+      </c>
+      <c r="B12" t="str">
+        <v>TE531-108</v>
+      </c>
+      <c r="C12" t="str">
+        <v>116993194690</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Oil Seal</v>
+      </c>
+      <c r="B13" t="str">
+        <v>DW65.02510-0001</v>
+      </c>
+      <c r="C13" t="str">
+        <v>543934960817</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>O-Ring</v>
+      </c>
+      <c r="B14" t="str">
+        <v>HY1589857</v>
+      </c>
+      <c r="C14" t="str">
+        <v>850999170937</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Nut</v>
+      </c>
+      <c r="B15" t="str">
+        <v>KO01593-11411</v>
+      </c>
+      <c r="C15" t="str">
+        <v>362518226825</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Check Valve</v>
+      </c>
+      <c r="B16" t="str">
+        <v>800053337</v>
+      </c>
+      <c r="C16" t="str">
+        <v>957782531601</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Bolt</v>
+      </c>
+      <c r="B17" t="str">
+        <v>GN112507GT</v>
+      </c>
+      <c r="C17" t="str">
+        <v>887571576233</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Valve Bleedback .495x.835</v>
+      </c>
+      <c r="B18" t="str">
+        <v>KEP-2203C-1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>273650298813</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Ignition Coil Harness</v>
+      </c>
+      <c r="B19" t="str">
+        <v>a22030100ux8170</v>
+      </c>
+      <c r="C19" t="str">
+        <v>455446318400</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coil - 24 Volt</v>
+      </c>
+      <c r="B20" t="str">
+        <v>RA520-950-003</v>
+      </c>
+      <c r="C20" t="str">
+        <v>612541813879</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Plate Clutch</v>
+      </c>
+      <c r="B21" t="str">
+        <v>KOAS35633-3410</v>
+      </c>
+      <c r="C21" t="str">
+        <v>257434231762</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Seal - Steer Hub</v>
+      </c>
+      <c r="B22" t="str">
+        <v>CL4303152</v>
+      </c>
+      <c r="C22" t="str">
+        <v>487659778997</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Cup 4 44x0 95</v>
+      </c>
+      <c r="B23" t="str">
+        <v>HY0230324</v>
+      </c>
+      <c r="C23" t="str">
+        <v>421871822089</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Seal - Felt</v>
+      </c>
+      <c r="B24" t="str">
+        <v>CR085582</v>
+      </c>
+      <c r="C24" t="str">
+        <v>553717623772</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Pin - Dowel</v>
+      </c>
+      <c r="B25" t="str">
+        <v>CR061011</v>
+      </c>
+      <c r="C25" t="str">
+        <v>386986686219</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>O - Ring</v>
+      </c>
+      <c r="B26" t="str">
+        <v>HY1589860</v>
+      </c>
+      <c r="C26" t="str">
+        <v>207236476335</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Seal Kit - Lift Cylinder</v>
+      </c>
+      <c r="B27" t="str">
+        <v>DWD512303</v>
+      </c>
+      <c r="C27" t="str">
+        <v>902912739245</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Locknut - Wheel Bearing</v>
+      </c>
+      <c r="B28" t="str">
+        <v>NI40262-FJ100</v>
+      </c>
+      <c r="C28" t="str">
+        <v>825502465759</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Needle Thrust Bearing</v>
+      </c>
+      <c r="B29" t="str">
+        <v>CR065014-001</v>
+      </c>
+      <c r="C29" t="str">
+        <v>808435732264</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Seal Oil</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TY41182-30510-71</v>
+      </c>
+      <c r="C30" t="str">
+        <v>346681538885</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Race - Inner</v>
+      </c>
+      <c r="B31" t="str">
+        <v>CR065063</v>
+      </c>
+      <c r="C31" t="str">
+        <v>210374412274</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Seal Kit - Lift Cylinder</v>
+      </c>
+      <c r="B32" t="str">
+        <v>HY1358969</v>
+      </c>
+      <c r="C32" t="str">
+        <v>706005957209</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Switch - Seat</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TY53736-U1090-71</v>
+      </c>
+      <c r="C33" t="str">
+        <v>683454077909</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>V Belt</v>
+      </c>
+      <c r="B34" t="str">
+        <v>7370</v>
+      </c>
+      <c r="C34" t="str">
+        <v>815915738017</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Strap - Static Ground</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SY9965</v>
+      </c>
+      <c r="C35" t="str">
+        <v>073985217828</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>O - Ring</v>
+      </c>
+      <c r="B36" t="str">
+        <v>HY1610508</v>
+      </c>
+      <c r="C36" t="str">
+        <v>664895091419</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Bearing - Needle</v>
+      </c>
+      <c r="B37" t="str">
+        <v>CR065013-004</v>
+      </c>
+      <c r="C37" t="str">
+        <v>293542024822</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Nut</v>
+      </c>
+      <c r="B38" t="str">
+        <v>KO01593-11411</v>
+      </c>
+      <c r="C38" t="str">
+        <v>761472633506</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Hook Group - Lower</v>
+      </c>
+      <c r="B39" t="str">
+        <v>CA204182</v>
+      </c>
+      <c r="C39" t="str">
+        <v>189268965530</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Bearing - Needle</v>
+      </c>
+      <c r="B40" t="str">
+        <v>KO0307-15-11930</v>
+      </c>
+      <c r="C40" t="str">
+        <v>728628456402</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Wheel - Poly 4x2.5x2.047x59</v>
+      </c>
+      <c r="B41" t="str">
+        <v>TY00590-04780-71-THO</v>
+      </c>
+      <c r="C41" t="str">
+        <v>870116455387</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Emergecy Brake Mit/Cat</v>
+      </c>
+      <c r="B42" t="str">
+        <v>91E46-00119</v>
+      </c>
+      <c r="C42" t="str">
+        <v>086083280761</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Cable Brake</v>
+      </c>
+      <c r="B43" t="str">
+        <v>CT360541</v>
+      </c>
+      <c r="C43" t="str">
+        <v>503263673137</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E43">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/product-labels.xlsx
+++ b/data/product-labels.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,9 +416,26 @@
         <v>Quantity</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Test product</v>
+      </c>
+      <c r="B2" t="str">
+        <v>T-56443-23-71</v>
+      </c>
+      <c r="C2" t="str">
+        <v>488276718573</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>